--- a/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -478,7 +478,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-28. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -663,9 +663,10 @@
           <t>Q1_2019</t>
         </is>
       </c>
-      <c r="B6">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>92</v>
@@ -792,9 +793,10 @@
           <t>Q2_2019</t>
         </is>
       </c>
-      <c r="B11">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>108</v>
@@ -921,9 +923,10 @@
           <t>Q3_2019</t>
         </is>
       </c>
-      <c r="B16">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>117</v>
@@ -1050,9 +1053,10 @@
           <t>Q4_2019</t>
         </is>
       </c>
-      <c r="B21">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>118</v>
@@ -1179,9 +1183,10 @@
           <t>Q1_2020</t>
         </is>
       </c>
-      <c r="B26">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>119</v>
@@ -1308,9 +1313,10 @@
           <t>Q2_2020</t>
         </is>
       </c>
-      <c r="B31">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>119</v>
@@ -1437,9 +1443,10 @@
           <t>Q3_2020</t>
         </is>
       </c>
-      <c r="B36">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C36" s="4" t="n">
         <v>119</v>
@@ -1566,9 +1573,10 @@
           <t>Q4_2020</t>
         </is>
       </c>
-      <c r="B41">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>120</v>
@@ -1695,9 +1703,10 @@
           <t>Q1_2021</t>
         </is>
       </c>
-      <c r="B46">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C46" s="4" t="n">
         <v>121</v>
@@ -1824,9 +1833,10 @@
           <t>Q2_2021</t>
         </is>
       </c>
-      <c r="B51">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>121</v>
@@ -1953,9 +1963,10 @@
           <t>Q3_2021</t>
         </is>
       </c>
-      <c r="B56">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C56" s="4" t="n">
         <v>121</v>
@@ -2082,9 +2093,10 @@
           <t>Q4_2021</t>
         </is>
       </c>
-      <c r="B61">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C61" s="4" t="n">
         <v>122</v>
@@ -2211,9 +2223,10 @@
           <t>Q1_2022</t>
         </is>
       </c>
-      <c r="B66">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C66" s="4" t="n">
         <v>123</v>
@@ -2340,9 +2353,10 @@
           <t>Q2_2022</t>
         </is>
       </c>
-      <c r="B71">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C71" s="4" t="n">
         <v>123</v>
@@ -2469,9 +2483,10 @@
           <t>Q3_2022</t>
         </is>
       </c>
-      <c r="B76">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C76" s="4" t="n">
         <v>126</v>
@@ -2598,9 +2613,10 @@
           <t>Q4_2022</t>
         </is>
       </c>
-      <c r="B81">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C81" s="4" t="n">
         <v>128</v>
@@ -2727,9 +2743,10 @@
           <t>Q1_2023</t>
         </is>
       </c>
-      <c r="B86">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C86" s="4" t="n">
         <v>128</v>
@@ -2856,9 +2873,10 @@
           <t>Q2_2023</t>
         </is>
       </c>
-      <c r="B91">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C91" s="4" t="n">
         <v>128</v>
@@ -2985,9 +3003,10 @@
           <t>Q3_2023</t>
         </is>
       </c>
-      <c r="B96">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C96" s="4" t="n">
         <v>128</v>
@@ -3114,9 +3133,10 @@
           <t>Q4_2023</t>
         </is>
       </c>
-      <c r="B101">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C101" s="4" t="n">
         <v>128</v>
@@ -3243,9 +3263,10 @@
           <t>Q1_2024</t>
         </is>
       </c>
-      <c r="B106">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C106" s="4" t="n">
         <v>128</v>
@@ -3372,9 +3393,10 @@
           <t>Q2_2024</t>
         </is>
       </c>
-      <c r="B111">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
         <v>128</v>
@@ -3501,9 +3523,10 @@
           <t>Q3_2024</t>
         </is>
       </c>
-      <c r="B116">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C116" s="4" t="n">
         <v>128</v>
@@ -3630,9 +3653,10 @@
           <t>Q4_2024</t>
         </is>
       </c>
-      <c r="B121">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C121" s="4" t="n">
         <v>129</v>
@@ -3759,9 +3783,10 @@
           <t>Q1_2025</t>
         </is>
       </c>
-      <c r="B126">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C126" s="4" t="n">
         <v>130</v>
@@ -3888,9 +3913,10 @@
           <t>Q2_2025</t>
         </is>
       </c>
-      <c r="B131">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C131" s="4" t="n">
         <v>130</v>
@@ -4017,9 +4043,10 @@
           <t>Q3_2025</t>
         </is>
       </c>
-      <c r="B136">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C136" s="4" t="n">
         <v>130</v>
@@ -4146,9 +4173,10 @@
           <t>Q4_2025</t>
         </is>
       </c>
-      <c r="B141">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C141" s="4" t="n">
         <v>129</v>
@@ -4275,9 +4303,10 @@
           <t>Q1_2026</t>
         </is>
       </c>
-      <c r="B146">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C146" s="4" t="n">
         <v>129</v>
@@ -4404,9 +4433,10 @@
           <t>Q2_2026</t>
         </is>
       </c>
-      <c r="B151">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C151" s="4" t="n">
         <v>128</v>
@@ -4533,9 +4563,10 @@
           <t>Q3_2026</t>
         </is>
       </c>
-      <c r="B156">
-        <f>== PERIOD TOTAL ===</f>
-        <v/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>=== PERIOD TOTAL ===</t>
+        </is>
       </c>
       <c r="C156" s="4" t="n">
         <v>128</v>

--- a/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -471,14 +471,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Scope: 130 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
+          <t>Scope: 129 artists (first-submission cohort) x 31 quarters, Q1 2019 – Q3 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-31. Source: delivery130/04_Datasets — figures equal those cells.</t>
+          <t>Generated 2026-09-01. Source: delivery130/04_Datasets — figures equal those cells.</t>
         </is>
       </c>
     </row>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>178500000</v>
+        <v>177000000</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>119000</v>
+        <v>118000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3570000</v>
+        <v>3540000</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1137,13 +1137,13 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>59500000</v>
+        <v>59000000</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>39666.67</v>
+        <v>39333.33</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5950000</v>
+        <v>5900000</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3966.67</v>
+        <v>3933.33</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>247520000</v>
+        <v>245440000</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>165013.33</v>
+        <v>163626.67</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>178500000</v>
+        <v>177000000</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>119000</v>
+        <v>118000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3570000</v>
+        <v>3540000</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>59500000</v>
+        <v>59000000</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>39666.67</v>
+        <v>39333.33</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5950000</v>
+        <v>5900000</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3966.67</v>
+        <v>3933.33</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>247520000</v>
+        <v>245440000</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>165013.33</v>
+        <v>163626.67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>178500000</v>
+        <v>177000000</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>119000</v>
+        <v>118000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3570000</v>
+        <v>3540000</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>59500000</v>
+        <v>59000000</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>39666.67</v>
+        <v>39333.33</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5950000</v>
+        <v>5900000</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3966.67</v>
+        <v>3933.33</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>247520000</v>
+        <v>245440000</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>165013.33</v>
+        <v>163626.67</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>180000000</v>
+        <v>178500000</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>120000</v>
+        <v>119000</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>3600000</v>
+        <v>3570000</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>60000000</v>
+        <v>59500000</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>40000</v>
+        <v>39666.67</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>6000000</v>
+        <v>5950000</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>4000</v>
+        <v>3966.67</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>249600000</v>
+        <v>247520000</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>166400</v>
+        <v>165013.33</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>181500000</v>
+        <v>180000000</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>121000</v>
+        <v>120000</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>3630000</v>
+        <v>3600000</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1657,13 +1657,13 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>60500000</v>
+        <v>60000000</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>40333.33</v>
+        <v>40000</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>6050000</v>
+        <v>6000000</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>4033.33</v>
+        <v>4000</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>251680000</v>
+        <v>249600000</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>167786.67</v>
+        <v>166400</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>181500000</v>
+        <v>180000000</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>121000</v>
+        <v>120000</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>3630000</v>
+        <v>3600000</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1787,13 +1787,13 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>60500000</v>
+        <v>60000000</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>40333.33</v>
+        <v>40000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1813,13 +1813,13 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>6050000</v>
+        <v>6000000</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4033.33</v>
+        <v>4000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>251680000</v>
+        <v>249600000</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>167786.67</v>
+        <v>166400</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1865,13 +1865,13 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>181500000</v>
+        <v>180000000</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>121000</v>
+        <v>120000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>3630000</v>
+        <v>3600000</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60500000</v>
+        <v>60000000</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>40333.33</v>
+        <v>40000</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>6050000</v>
+        <v>6000000</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4033.33</v>
+        <v>4000</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>251680000</v>
+        <v>249600000</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>167786.67</v>
+        <v>166400</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>183000000</v>
+        <v>181500000</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>122000</v>
+        <v>121000</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2021,13 +2021,13 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>3660000</v>
+        <v>3630000</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2047,13 +2047,13 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>61000000</v>
+        <v>60500000</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>40666.67</v>
+        <v>40333.33</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>6100000</v>
+        <v>6050000</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4066.67</v>
+        <v>4033.33</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>253760000</v>
+        <v>251680000</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>169173.33</v>
+        <v>167786.67</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>184500000</v>
+        <v>183000000</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>123000</v>
+        <v>122000</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>3690000</v>
+        <v>3660000</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>61500000</v>
+        <v>61000000</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>41000</v>
+        <v>40666.67</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>6150000</v>
+        <v>6100000</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4100</v>
+        <v>4066.67</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2229,13 +2229,13 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>255840000</v>
+        <v>253760000</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>170560</v>
+        <v>169173.33</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2255,13 +2255,13 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>184500000</v>
+        <v>183000000</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>123000</v>
+        <v>122000</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>3690000</v>
+        <v>3660000</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2307,13 +2307,13 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>61500000</v>
+        <v>61000000</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>41000</v>
+        <v>40666.67</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>6150000</v>
+        <v>6100000</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4100</v>
+        <v>4066.67</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2359,13 +2359,13 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>255840000</v>
+        <v>253760000</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>170560</v>
+        <v>169173.33</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>189000000</v>
+        <v>187500000</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>126000</v>
+        <v>125000</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3780000</v>
+        <v>3750000</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2520</v>
+        <v>2500</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>63000000</v>
+        <v>62500000</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>42000</v>
+        <v>41666.67</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>6300000</v>
+        <v>6250000</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4200</v>
+        <v>4166.67</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>262080000</v>
+        <v>260000000</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>174720</v>
+        <v>173333.33</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2671,13 +2671,13 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2723,13 +2723,13 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2749,13 +2749,13 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2827,13 +2827,13 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2879,13 +2879,13 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2905,13 +2905,13 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3061,13 +3061,13 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3113,13 +3113,13 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3217,13 +3217,13 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3399,13 +3399,13 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3451,13 +3451,13 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3529,13 +3529,13 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3555,13 +3555,13 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>193500000</v>
+        <v>192000000</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>129000</v>
+        <v>128000</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3581,13 +3581,13 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>3870000</v>
+        <v>3840000</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2580</v>
+        <v>2560</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>64500000</v>
+        <v>64000000</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>43000</v>
+        <v>42666.67</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3633,13 +3633,13 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>6450000</v>
+        <v>6400000</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4300</v>
+        <v>4266.67</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3659,13 +3659,13 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>268320000</v>
+        <v>266240000</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>178880</v>
+        <v>177493.33</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3685,13 +3685,13 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>195000000</v>
+        <v>193500000</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>130000</v>
+        <v>129000</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>3900000</v>
+        <v>3870000</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2600</v>
+        <v>2580</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3737,13 +3737,13 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>65000000</v>
+        <v>64500000</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>43333.33</v>
+        <v>43000</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>6500000</v>
+        <v>6450000</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4333.33</v>
+        <v>4300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3789,13 +3789,13 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>270400000</v>
+        <v>268320000</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>180266.67</v>
+        <v>178880</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>195000000</v>
+        <v>193500000</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>130000</v>
+        <v>129000</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3841,13 +3841,13 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>3900000</v>
+        <v>3870000</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2600</v>
+        <v>2580</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>65000000</v>
+        <v>64500000</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>43333.33</v>
+        <v>43000</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3893,13 +3893,13 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>6500000</v>
+        <v>6450000</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4333.33</v>
+        <v>4300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -3919,13 +3919,13 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>270400000</v>
+        <v>268320000</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>180266.67</v>
+        <v>178880</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>195000000</v>
+        <v>193500000</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>130000</v>
+        <v>129000</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>3900000</v>
+        <v>3870000</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2600</v>
+        <v>2580</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>65000000</v>
+        <v>64500000</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>43333.33</v>
+        <v>43000</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>6500000</v>
+        <v>6450000</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4333.33</v>
+        <v>4300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4049,13 +4049,13 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>270400000</v>
+        <v>268320000</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>180266.67</v>
+        <v>178880</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4075,13 +4075,13 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>193500000</v>
+        <v>192000000</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>129000</v>
+        <v>128000</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>3870000</v>
+        <v>3840000</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2580</v>
+        <v>2560</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4127,13 +4127,13 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>64500000</v>
+        <v>64000000</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43000</v>
+        <v>42666.67</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>6450000</v>
+        <v>6400000</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4300</v>
+        <v>4266.67</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4179,13 +4179,13 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>268320000</v>
+        <v>266240000</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>178880</v>
+        <v>177493.33</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4205,13 +4205,13 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>193500000</v>
+        <v>192000000</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>129000</v>
+        <v>128000</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4231,13 +4231,13 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>3870000</v>
+        <v>3840000</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2580</v>
+        <v>2560</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>64500000</v>
+        <v>64000000</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>43000</v>
+        <v>42666.67</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>6450000</v>
+        <v>6400000</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4300</v>
+        <v>4266.67</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>268320000</v>
+        <v>266240000</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>178880</v>
+        <v>177493.33</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -4361,13 +4361,13 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4387,13 +4387,13 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4465,13 +4465,13 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>192000000</v>
+        <v>190500000</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -4491,13 +4491,13 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>3840000</v>
+        <v>3810000</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2560</v>
+        <v>2540</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>64000000</v>
+        <v>63500000</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>42666.67</v>
+        <v>42333.33</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -4543,13 +4543,13 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>6400000</v>
+        <v>6350000</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4266.67</v>
+        <v>4233.33</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4569,13 +4569,13 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>266240000</v>
+        <v>264160000</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>177493.33</v>
+        <v>176106.67</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>

--- a/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
+++ b/delivery130/03_Excel_Deliveries/4_Hosting_Production_Costs.xlsx
@@ -571,7 +571,7 @@
         <v>138000000</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>92000</v>
+        <v>449628.57</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>2760000</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1840</v>
+        <v>8992.57</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         <v>46000000</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>30666.67</v>
+        <v>149876.19</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>4600000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3066.67</v>
+        <v>14987.62</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
         <v>191360000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>127573.33</v>
+        <v>623484.95</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         <v>162000000</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>108000</v>
+        <v>527824.84</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>3240000</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2160</v>
+        <v>10556.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>54000000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>36000</v>
+        <v>175941.61</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>5400000</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3600</v>
+        <v>17594.16</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>224640000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>149760</v>
+        <v>731917.11</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>175500000</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>117000</v>
+        <v>571810.24</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>3510000</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>2340</v>
+        <v>11436.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>58500000</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>39000</v>
+        <v>190603.41</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>5850000</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3900</v>
+        <v>19060.34</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>243360000</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>162240</v>
+        <v>792910.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         <v>177000000</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>118000</v>
+        <v>576697.51</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>3540000</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2360</v>
+        <v>11533.95</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>59000000</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>39333.33</v>
+        <v>192232.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>5900000</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3933.33</v>
+        <v>19223.25</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>245440000</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>163626.67</v>
+        <v>799687.21</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>177000000</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>118000</v>
+        <v>493297.29</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>3540000</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>2360</v>
+        <v>9865.950000000001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>59000000</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>39333.33</v>
+        <v>164432.43</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>5900000</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3933.33</v>
+        <v>16443.24</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>245440000</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>163626.67</v>
+        <v>684038.91</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>177000000</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>118000</v>
+        <v>493297.29</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>3540000</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2360</v>
+        <v>9865.950000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>59000000</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>39333.33</v>
+        <v>164432.43</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>5900000</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3933.33</v>
+        <v>16443.24</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>245440000</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>163626.67</v>
+        <v>684038.91</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>177000000</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>118000</v>
+        <v>493297.29</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>3540000</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2360</v>
+        <v>9865.950000000001</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>59000000</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>39333.33</v>
+        <v>164432.43</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>5900000</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3933.33</v>
+        <v>16443.24</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>245440000</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>163626.67</v>
+        <v>684038.91</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>178500000</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>119000</v>
+        <v>497477.77</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>3570000</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2380</v>
+        <v>9949.559999999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>59500000</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>39666.67</v>
+        <v>165825.92</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>5950000</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>3966.67</v>
+        <v>16582.59</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>247520000</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>165013.33</v>
+        <v>689835.85</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>180000000</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>120000</v>
+        <v>448709.96</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>3600000</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2400</v>
+        <v>8974.200000000001</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>60000000</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>40000</v>
+        <v>149569.99</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>6000000</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>4000</v>
+        <v>14957</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>249600000</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>166400</v>
+        <v>622211.14</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>180000000</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>120000</v>
+        <v>448709.96</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>3600000</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2400</v>
+        <v>8974.200000000001</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>60000000</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>40000</v>
+        <v>149569.99</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>6000000</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4000</v>
+        <v>14957</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>249600000</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>166400</v>
+        <v>622211.14</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>180000000</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>120000</v>
+        <v>448709.96</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>3600000</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2400</v>
+        <v>8974.200000000001</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>60000000</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>40000</v>
+        <v>149569.99</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>6000000</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4000</v>
+        <v>14957</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>249600000</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>166400</v>
+        <v>622211.14</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>181500000</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>121000</v>
+        <v>452449.21</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>3630000</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2420</v>
+        <v>9048.98</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>60500000</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>40333.33</v>
+        <v>150816.4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>6050000</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4033.33</v>
+        <v>15081.64</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>251680000</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>167786.67</v>
+        <v>627396.24</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>183000000</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>122000</v>
+        <v>429597.63</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>3660000</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2440</v>
+        <v>8591.950000000001</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>61000000</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>40666.67</v>
+        <v>143199.21</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>6100000</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>4066.67</v>
+        <v>14319.92</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>253760000</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>169173.33</v>
+        <v>595708.72</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>183000000</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>122000</v>
+        <v>429597.63</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>3660000</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>2440</v>
+        <v>8591.950000000001</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>61000000</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>40666.67</v>
+        <v>143199.21</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>6100000</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4066.67</v>
+        <v>14319.92</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>253760000</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>169173.33</v>
+        <v>595708.72</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>187500000</v>
+        <v>186000000</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>125000</v>
+        <v>436640.22</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>3750000</v>
+        <v>3720000</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>2500</v>
+        <v>8732.799999999999</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>62500000</v>
+        <v>62000000</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>41666.67</v>
+        <v>145546.74</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2463,13 +2463,13 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>6250000</v>
+        <v>6200000</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>4166.67</v>
+        <v>14554.67</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2489,13 +2489,13 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>260000000</v>
+        <v>257920000</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>173333.33</v>
+        <v>605474.4399999999</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>190500000</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>127000</v>
+        <v>447204.09</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>3810000</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>2540</v>
+        <v>8944.08</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>63500000</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>42333.33</v>
+        <v>149068.03</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>6350000</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>4233.33</v>
+        <v>14906.8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>264160000</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>176106.67</v>
+        <v>620123.01</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>190500000</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>127000</v>
+        <v>295348.84</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>3810000</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2540</v>
+        <v>5906.98</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>63500000</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>42333.33</v>
+        <v>98449.61</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>6350000</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4233.33</v>
+        <v>9844.959999999999</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>264160000</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>176106.67</v>
+        <v>409550.39</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>190500000</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>127000</v>
+        <v>295348.84</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>3810000</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2540</v>
+        <v>5906.98</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>63500000</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>42333.33</v>
+        <v>98449.61</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2859,7 +2859,7 @@
         <v>6350000</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>4233.33</v>
+        <v>9844.959999999999</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>264160000</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>176106.67</v>
+        <v>409550.39</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>190500000</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>127000</v>
+        <v>295348.84</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>3810000</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2540</v>
+        <v>5906.98</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>63500000</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>42333.33</v>
+        <v>98449.61</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>6350000</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>4233.33</v>
+        <v>9844.959999999999</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>264160000</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>176106.67</v>
+        <v>409550.39</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>190500000</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>127000</v>
+        <v>295348.84</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>3810000</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2540</v>
+        <v>5906.98</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>63500000</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>42333.33</v>
+        <v>98449.61</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>6350000</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4233.33</v>
+        <v>9844.959999999999</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>264160000</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>176106.67</v>
+        <v>409550.39</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>190500000</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>127000</v>
+        <v>128890.39</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>3810000</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2540</v>
+        <v>2577.81</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>63500000</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>42333.33</v>
+        <v>42963.46</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>6350000</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>4233.33</v>
+        <v>4296.35</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>264160000</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>176106.67</v>
+        <v>178728.01</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>190500000</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>127000</v>
+        <v>128890.39</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>3810000</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2540</v>
+        <v>2577.81</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>63500000</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>42333.33</v>
+        <v>42963.46</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>6350000</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>4233.33</v>
+        <v>4296.35</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>264160000</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>176106.67</v>
+        <v>178728.01</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>190500000</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>127000</v>
+        <v>128890.39</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>3810000</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2540</v>
+        <v>2577.81</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>63500000</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>42333.33</v>
+        <v>42963.46</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>6350000</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>4233.33</v>
+        <v>4296.35</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>264160000</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>176106.67</v>
+        <v>178728.01</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>192000000</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>128000</v>
+        <v>129905.28</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>3840000</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2560</v>
+        <v>2598.11</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>64000000</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>42666.67</v>
+        <v>43301.76</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>6400000</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4266.67</v>
+        <v>4330.18</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>266240000</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>177493.33</v>
+        <v>180135.32</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>193500000</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>129000</v>
+        <v>126470.59</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>3870000</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2580</v>
+        <v>2529.41</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>64500000</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>43000</v>
+        <v>42156.86</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>6450000</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4300</v>
+        <v>4215.69</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>268320000</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>178880</v>
+        <v>175372.55</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>193500000</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>129000</v>
+        <v>126470.59</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>3870000</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2580</v>
+        <v>2529.41</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>64500000</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>43000</v>
+        <v>42156.86</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>6450000</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4300</v>
+        <v>4215.69</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>268320000</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>178880</v>
+        <v>175372.55</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>193500000</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>129000</v>
+        <v>126470.59</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>3870000</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2580</v>
+        <v>2529.41</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>64500000</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>43000</v>
+        <v>42156.86</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>6450000</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4300</v>
+        <v>4215.69</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>268320000</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>178880</v>
+        <v>175372.55</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>192000000</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>128000</v>
+        <v>125490.2</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>3840000</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>2560</v>
+        <v>2509.8</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>64000000</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>42666.67</v>
+        <v>41830.07</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>6400000</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>4266.67</v>
+        <v>4183.01</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>266240000</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>177493.33</v>
+        <v>174013.07</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>192000000</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>128000</v>
+        <v>125490.2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>3840000</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2560</v>
+        <v>2509.8</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>64000000</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>42666.67</v>
+        <v>41830.07</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>6400000</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>4266.67</v>
+        <v>4183.01</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>266240000</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>177493.33</v>
+        <v>174013.07</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>190500000</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>127000</v>
+        <v>124509.8</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>3810000</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2540</v>
+        <v>2490.2</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>63500000</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>42333.33</v>
+        <v>41503.27</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>6350000</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4233.33</v>
+        <v>4150.33</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>264160000</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>176106.67</v>
+        <v>172653.59</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>190500000</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>127000</v>
+        <v>124509.8</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>3810000</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>2540</v>
+        <v>2490.2</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>63500000</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>42333.33</v>
+        <v>41503.27</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>6350000</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>4233.33</v>
+        <v>4150.33</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>264160000</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>176106.67</v>
+        <v>172653.59</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
